--- a/imdb_top_250.xlsx
+++ b/imdb_top_250.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>小行星的好坏美丑</t>
+          <t>"The Proud Family" The Good, the Bad, and the Ugly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>阿拉伯的劳伦斯</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>大卫·里恩</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>骗中骗</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>乔治·罗伊·希尔</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>双重赔偿</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>比利·怀德</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>飞屋环游记</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>彼特·道格特</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>夺宝奇兵3</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>史蒂文·斯皮尔伯格</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>绿皮书</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>彼得·法雷里</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>巨蟒与圣杯</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>特瑞·吉列姆</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>蝙蝠侠：侠影之谜</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>克里斯托弗·诺兰</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>死亡空间：坍塌</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>Chuck Patton</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>小鞋子</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>马基德·马基迪</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>不可饶恕</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>克林特·伊斯特伍德</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>哈尔的移动城堡</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>宫崎骏</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>彗星美人</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>约瑟夫·L·曼凯维奇</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>美丽心灵</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>朗·霍华德</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>赌城风云</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>马丁·斯科塞斯</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>大逃亡</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>约翰·斯特奇斯</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>华尔街之狼</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>马丁·斯科塞斯</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>潘神的迷宫</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>吉尔莫·德尔·托罗</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>谜一样的双眼</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>比利·雷</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>血色将至</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>保罗·托马斯·安德森</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>两杆大烟枪</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>盖·里奇</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>龙猫</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>宫崎骏</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>愤怒的公牛</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>马丁·斯科塞斯</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>纽伦堡的审判</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>斯坦利·克雷默</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>碧血金沙</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>约翰·休斯顿</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>电话谋杀案</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>阿尔弗雷德·希区柯克</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>三块广告牌</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>马丁·麦克唐纳</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>禁闭岛</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>马丁·斯科塞斯</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>淘金记</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>查理·卓别林</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>唐人街</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>罗曼·波兰斯基</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>我的父亲，我的儿子</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>查恩·厄尔马克</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>老无所依</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>伊桑·科恩</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>制作《V字仇杀队》：自由永在</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>加雷思·大卫-劳埃德</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>头脑特工队</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>彼特·道格特</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>第七封印</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>英格玛·伯格曼</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>象人</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>大卫·林奇</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -4740,22 +4740,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>怪形</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Warrior</t>
+          <t>The Thing</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>约翰·卡朋特</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>1982</t>
         </is>
       </c>
     </row>
@@ -4767,22 +4767,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>勇士</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>The Thing</t>
+          <t>Warrior</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>加文·欧康诺</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2011</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>第六感</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>M·奈特·沙马兰</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>猜火车</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>丹尼·博伊尔</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -4848,22 +4848,22 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>侏罗纪公园</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Soul</t>
+          <t>Jurassic Park</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>史蒂文·斯皮尔伯格</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1993</t>
         </is>
       </c>
     </row>
@@ -4875,22 +4875,22 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>快乐的阿南</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Jurassic Park</t>
+          <t>Anand</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>西里斯科什·慕克吉</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1971</t>
         </is>
       </c>
     </row>
@@ -4902,22 +4902,22 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>心灵奇旅</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Anand</t>
+          <t>Soul</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>彼特·道格特</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>2020</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>楚门的世界</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>彼得·威尔</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>克劳斯：圣诞节的秘密</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>塞尔希奥·巴勃罗斯</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>乱世佳人</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>维克多·弗莱明</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>海底总动员</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>安德鲁·斯坦顿</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>野草莓</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>英格玛·伯格曼</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -5064,22 +5064,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>跟踪者</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Blade Runner</t>
+          <t>Stalker</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>丽兹·弗德兰德</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1979</t>
         </is>
       </c>
     </row>
@@ -5091,22 +5091,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>银翼杀手</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Stalker</t>
+          <t>Blade Runner</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>雷德利·斯科特</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1982</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>杀死比尔</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>昆汀·塔伦蒂诺</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>灵光血影</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>桂河大桥</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>大卫·里恩</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>冰血暴</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>乔尔·科恩</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>房间</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>伦尼·阿伯拉罕森</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>第三人</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>卡罗尔·里德</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>老爷车</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>克林特·伊斯特伍德</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>乡间趣事</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>码头风云</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>伊利亚·卡赞</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>东京物语</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>小津安二郎</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>猎鹿人</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>迈克尔·西米诺</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>因父之名</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>吉姆·谢里丹</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>秋日奏鸣曲：制作特辑</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>玛丽和马克思</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>亚当·艾略特</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>布达佩斯大饭店</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>韦斯·安德森</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>消失的爱人</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>大卫·芬奇</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>爱在黎明破晓前</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>理查德·林克莱特</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>血战钢锯岭</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>梅尔·吉布森</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>猫鼠游戏</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>史蒂文·斯皮尔伯格</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>调音师</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>斯里兰姆·拉格万</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>假面</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>英格玛·伯格曼</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>囚徒</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>丹尼斯·维伦纽瓦</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>谋杀绿脚趾</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>乔尔·科恩</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>你逃我也逃</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>恩斯特·刘别谦</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>福尔摩斯二世</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>巴斯特·基顿</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>将军号</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>巴斯特·基顿</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>驯龙高手</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>迪恩·德布洛斯</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -5847,22 +5847,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>极速车王</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>The Bandit</t>
+          <t>Ford v Ferrari</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>詹姆斯·曼高德</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2019</t>
         </is>
       </c>
     </row>
@@ -5874,22 +5874,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
+          <t>The Bandit</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>The Bandit</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
           <t>not found</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Ford v Ferrari</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1996</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>为奴十二年</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>史蒂夫·麦奎因</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>巴里·林登</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>斯坦利·库布里克</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>史密斯先生到华盛顿</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>弗兰克·卡普拉</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>疯狂的麦克斯4：狂暴之路</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>乔治·米勒</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>流浪者之歌</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>埃米尔·库斯图里卡</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>百万美元宝贝</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>克林特·伊斯特伍德</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>电视台风云</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>西德尼·吕美特</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>死亡诗社</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>彼得·威尔</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>伴我同行</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>罗伯·莱纳</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>宾虚</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>威廉·惠勒</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>哈利·波特与死亡圣器(下)</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>大卫·叶茨</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>铁窗喋血</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>斯图尔特·罗森博格</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>忠犬八公的故事</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>拉斯·霍尔斯道姆</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>野战排</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>奥利佛·斯通</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>小姐</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>朴赞郁</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -6306,22 +6306,22 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>荒野生存</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Into the Wild</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>西恩·潘</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2007</t>
         </is>
       </c>
     </row>
@@ -6333,22 +6333,22 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>金刚狼3：殊死一战</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Into the Wild</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>詹姆斯·曼高德</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2017</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>极速风流</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>朗·霍华德</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>恐惧的代价</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>亨利-乔治·克鲁佐</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>万世魔星</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>特瑞·琼斯</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>四百击</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>弗朗索瓦·特吕弗</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>聚焦</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>汤姆·麦卡锡</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>圣女贞德蒙难记</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>卡尔·西奥多·德莱叶</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -6522,22 +6522,22 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>怒火青春</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Hotel Rwanda</t>
+          <t>La Haine</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>马修·卡索维茨</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>1995</t>
         </is>
       </c>
     </row>
@@ -6549,22 +6549,22 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>卢旺达饭店</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>La Haine</t>
+          <t>Hotel Rwanda</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>特瑞·乔治</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2004</t>
         </is>
       </c>
     </row>
@@ -6576,22 +6576,22 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>爱情是狗娘</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Andrei Rublev</t>
+          <t>Amores Perros</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>亚历杭德罗·冈萨雷斯·伊纳里图</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>2000</t>
         </is>
       </c>
     </row>
@@ -6603,22 +6603,22 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>安德烈·卢布廖夫</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Amores Perros</t>
+          <t>Andrei Rublev</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>安德烈·塔可夫斯基</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1966</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>洛奇</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>约翰·G·艾维尔森</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>瓦塞浦黑帮(上)</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>阿努拉格·卡施亚普</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>怪兽电力公司</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>彼特·道格特</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>风之谷</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>宫崎骏</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -6738,22 +6738,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>蝴蝶梦</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Vikram Vedha</t>
+          <t>Rebecca</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>阿尔弗雷德·希区柯克</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>1940</t>
         </is>
       </c>
     </row>
@@ -6765,22 +6765,22 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>迷魂枭雄</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Rebecca</t>
+          <t>Vikram Vedha</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>Gayatri Joshi</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2017</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>男人的争斗</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>芭萨提的颜色</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>拉凯什·奥姆普拉卡西·梅赫拉</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>爱在日落黄昏时</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>理查德·林克莱特</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>花样年华</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>王家卫</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -6900,22 +6900,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>怒火救援</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Paris, Texas</t>
+          <t>Portrait of a Lady on Fire</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>托尼·斯科特</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>2019</t>
         </is>
       </c>
     </row>
@@ -6927,22 +6927,22 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>德州巴黎</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Portrait of a Lady on Fire</t>
+          <t>Paris, Texas</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>维姆·文德斯</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1984</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>一夜风流</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>弗兰克·卡普拉</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>韩版看不见的客人</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>相助</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>泰特·泰勒</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -7035,22 +7035,22 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>公主新娘</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Drishyam</t>
+          <t>The Princess Bride</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>罗伯·莱纳</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1987</t>
         </is>
       </c>
     </row>
@@ -7062,22 +7062,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>误杀瞒天记</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>The Princess Bride</t>
+          <t>Drishyam</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>尼西卡特·卡马特</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>2015</t>
         </is>
       </c>
     </row>
@@ -7089,7 +7089,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>Marxist Poetry: The Making of 'The Battle of Algiers'</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7116,22 +7116,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>Silent Voice 行动心理搜查官楯冈绘麻 第二季</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Winter Sleep</t>
+          <t>A Silent Voice: The Movie</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>栗山千明</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2016</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>金橘</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>萨萨·乌鲁沙泽</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
